--- a/Masters_Winners.xlsx
+++ b/Masters_Winners.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasgwartz/Desktop/Job/Projects/Python/Masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B611602-2D88-EC4F-B308-63A91B56D6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306D9928-16EE-264C-84F2-2616C7490076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="15900" xr2:uid="{0478EA40-DAE6-D342-BA5E-705AD7BF3F71}"/>
+    <workbookView xWindow="6640" yWindow="5160" windowWidth="28800" windowHeight="15900" xr2:uid="{0478EA40-DAE6-D342-BA5E-705AD7BF3F71}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="141">
   <si>
     <t>DOB</t>
   </si>
@@ -848,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12FEB8AC-D6F0-5441-ADB5-D048F64B0019}">
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="26.1640625" bestFit="1" customWidth="1"/>
@@ -2438,6 +2438,23 @@
       </c>
       <c r="E90" s="5"/>
     </row>
+    <row r="91" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A91" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E91" s="5">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
